--- a/docs/downloads/20260827_Johor_Teduh_Weekly_Update.xlsx
+++ b/docs/downloads/20260827_Johor_Teduh_Weekly_Update.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AI20"/>
+  <dimension ref="A2:AL20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -528,7 +528,10 @@
     <col width="9" customWidth="1" min="32" max="32"/>
     <col width="9" customWidth="1" min="33" max="33"/>
     <col width="9" customWidth="1" min="34" max="34"/>
-    <col width="46" customWidth="1" min="35" max="35"/>
+    <col width="9" customWidth="1" min="35" max="35"/>
+    <col width="9" customWidth="1" min="36" max="36"/>
+    <col width="9" customWidth="1" min="37" max="37"/>
+    <col width="46" customWidth="1" min="38" max="38"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -571,8 +574,11 @@
       <c r="AC3" s="3" t="n">
         <v>46248</v>
       </c>
-      <c r="AF3" s="4" t="n">
+      <c r="AF3" s="3" t="n">
         <v>46255</v>
+      </c>
+      <c r="AI3" s="4" t="n">
+        <v>46262</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -732,22 +738,37 @@
           <t>TOTAL %</t>
         </is>
       </c>
-      <c r="AF4" s="6" t="inlineStr">
+      <c r="AF4" s="5" t="inlineStr">
         <is>
           <t>NEW SALES</t>
         </is>
       </c>
-      <c r="AG4" s="6" t="inlineStr">
+      <c r="AG4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="AH4" s="6" t="inlineStr">
+      <c r="AH4" s="5" t="inlineStr">
         <is>
           <t>TOTAL %</t>
         </is>
       </c>
-      <c r="AI4" s="5" t="inlineStr">
+      <c r="AI4" s="6" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="AJ4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="AK4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL %</t>
+        </is>
+      </c>
+      <c r="AL4" s="5" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
@@ -793,6 +814,9 @@
       <c r="AG5" s="8" t="n"/>
       <c r="AH5" s="8" t="n"/>
       <c r="AI5" s="8" t="n"/>
+      <c r="AJ5" s="8" t="n"/>
+      <c r="AK5" s="8" t="n"/>
+      <c r="AL5" s="8" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
@@ -907,20 +931,31 @@
         <f>AD6/$D$6</f>
         <v/>
       </c>
-      <c r="AF6" s="13">
+      <c r="AF6" s="11">
         <f>AG6-AD6</f>
         <v/>
       </c>
-      <c r="AG6" s="13" t="n">
+      <c r="AG6" s="11" t="n">
         <v>302</v>
       </c>
-      <c r="AH6" s="14">
+      <c r="AH6" s="12">
         <f>AG6/$D$6</f>
         <v/>
       </c>
-      <c r="AI6" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 189, Block B: 113</t>
+      <c r="AI6" s="13">
+        <f>AJ6-AG6</f>
+        <v/>
+      </c>
+      <c r="AJ6" s="13" t="n">
+        <v>304</v>
+      </c>
+      <c r="AK6" s="14">
+        <f>AJ6/$D$6</f>
+        <v/>
+      </c>
+      <c r="AL6" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 190 units, Block B: 114 units</t>
         </is>
       </c>
     </row>
@@ -1037,20 +1072,31 @@
         <f>AD7/$D$7</f>
         <v/>
       </c>
-      <c r="AF7" s="13">
+      <c r="AF7" s="11">
         <f>AG7-AD7</f>
         <v/>
       </c>
-      <c r="AG7" s="13" t="n">
+      <c r="AG7" s="11" t="n">
         <v>954</v>
       </c>
-      <c r="AH7" s="14">
+      <c r="AH7" s="12">
         <f>AG7/$D$7</f>
         <v/>
       </c>
-      <c r="AI7" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 389, Block B: 371, Block C: 86, Block D: 108</t>
+      <c r="AI7" s="13">
+        <f>AJ7-AG7</f>
+        <v/>
+      </c>
+      <c r="AJ7" s="13" t="n">
+        <v>962</v>
+      </c>
+      <c r="AK7" s="14">
+        <f>AJ7/$D$7</f>
+        <v/>
+      </c>
+      <c r="AL7" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 394 units, Block B: 373 units, Block C: 87 units, Block D: 108 units</t>
         </is>
       </c>
     </row>
@@ -1167,18 +1213,29 @@
         <f>AD8/$D$8</f>
         <v/>
       </c>
-      <c r="AF8" s="13">
+      <c r="AF8" s="11">
         <f>AG8-AD8</f>
         <v/>
       </c>
-      <c r="AG8" s="13" t="n">
+      <c r="AG8" s="11" t="n">
         <v>48</v>
       </c>
-      <c r="AH8" s="14">
+      <c r="AH8" s="12">
         <f>AG8/$D$8</f>
         <v/>
       </c>
-      <c r="AI8" s="10" t="inlineStr">
+      <c r="AI8" s="13">
+        <f>AJ8-AG8</f>
+        <v/>
+      </c>
+      <c r="AJ8" s="13" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK8" s="14">
+        <f>AJ8/$D$8</f>
+        <v/>
+      </c>
+      <c r="AL8" s="10" t="inlineStr">
         <is>
           <t>Open sale for Block A (416 units) only; tracked against the full development</t>
         </is>
@@ -1297,20 +1354,31 @@
         <f>AD9/$D$9</f>
         <v/>
       </c>
-      <c r="AF9" s="13">
+      <c r="AF9" s="11">
         <f>AG9-AD9</f>
         <v/>
       </c>
-      <c r="AG9" s="13" t="n">
+      <c r="AG9" s="11" t="n">
         <v>1058</v>
       </c>
-      <c r="AH9" s="14">
+      <c r="AH9" s="12">
         <f>AG9/$D$9</f>
         <v/>
       </c>
-      <c r="AI9" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block 1A: 327, Block 1B: 340, Block 2A: 215, Block 2B: 176</t>
+      <c r="AI9" s="13">
+        <f>AJ9-AG9</f>
+        <v/>
+      </c>
+      <c r="AJ9" s="13" t="n">
+        <v>1062</v>
+      </c>
+      <c r="AK9" s="14">
+        <f>AJ9/$D$9</f>
+        <v/>
+      </c>
+      <c r="AL9" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Phase 1: 667 units, Phase 2: 395 units</t>
         </is>
       </c>
     </row>
@@ -1354,6 +1422,9 @@
       <c r="AG10" s="8" t="n"/>
       <c r="AH10" s="8" t="n"/>
       <c r="AI10" s="8" t="n"/>
+      <c r="AJ10" s="8" t="n"/>
+      <c r="AK10" s="8" t="n"/>
+      <c r="AL10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
@@ -1468,18 +1539,29 @@
         <f>AD11/$D$11</f>
         <v/>
       </c>
-      <c r="AF11" s="13">
+      <c r="AF11" s="11">
         <f>AG11-AD11</f>
         <v/>
       </c>
-      <c r="AG11" s="13" t="n">
+      <c r="AG11" s="11" t="n">
         <v>845</v>
       </c>
-      <c r="AH11" s="14">
+      <c r="AH11" s="12">
         <f>AG11/$D$11</f>
         <v/>
       </c>
-      <c r="AI11" s="10" t="inlineStr">
+      <c r="AI11" s="13">
+        <f>AJ11-AG11</f>
+        <v/>
+      </c>
+      <c r="AJ11" s="13" t="n">
+        <v>845</v>
+      </c>
+      <c r="AK11" s="14">
+        <f>AJ11/$D$11</f>
+        <v/>
+      </c>
+      <c r="AL11" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1598,20 +1680,31 @@
         <f>AD12/$D$12</f>
         <v/>
       </c>
-      <c r="AF12" s="13">
+      <c r="AF12" s="11">
         <f>AG12-AD12</f>
         <v/>
       </c>
-      <c r="AG12" s="13" t="n">
+      <c r="AG12" s="11" t="n">
         <v>1421</v>
       </c>
-      <c r="AH12" s="14">
+      <c r="AH12" s="12">
         <f>AG12/$D$12</f>
         <v/>
       </c>
-      <c r="AI12" s="10" t="inlineStr">
-        <is>
-          <t>Open sale for Block A, B &amp; D only. Block C (833 units) is not opened yet. Latest sales - Block A: 449, Block B1: 231, Block B2: 285, Block D1: 168, Block D2: 288</t>
+      <c r="AI12" s="13">
+        <f>AJ12-AG12</f>
+        <v/>
+      </c>
+      <c r="AJ12" s="13" t="n">
+        <v>1496</v>
+      </c>
+      <c r="AK12" s="14">
+        <f>AJ12/$D$12</f>
+        <v/>
+      </c>
+      <c r="AL12" s="10" t="inlineStr">
+        <is>
+          <t>Open sale for Block A, B &amp; D only. Block C (833 units) is not opened yet. Latest sales - Block A: 493 units, Block B: 530 units, Block D: 473 units</t>
         </is>
       </c>
     </row>
@@ -1728,20 +1821,31 @@
         <f>AD13/$D$13</f>
         <v/>
       </c>
-      <c r="AF13" s="13">
+      <c r="AF13" s="11">
         <f>AG13-AD13</f>
         <v/>
       </c>
-      <c r="AG13" s="13" t="n">
+      <c r="AG13" s="11" t="n">
         <v>1001</v>
       </c>
-      <c r="AH13" s="14">
+      <c r="AH13" s="12">
         <f>AG13/$D$13</f>
         <v/>
       </c>
-      <c r="AI13" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 403, Block B: 369, Block C: 229</t>
+      <c r="AI13" s="13">
+        <f>AJ13-AG13</f>
+        <v/>
+      </c>
+      <c r="AJ13" s="13" t="n">
+        <v>1006</v>
+      </c>
+      <c r="AK13" s="14">
+        <f>AJ13/$D$13</f>
+        <v/>
+      </c>
+      <c r="AL13" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 403 units, Block B: 369 units, Block C: 234 units</t>
         </is>
       </c>
     </row>
@@ -1858,20 +1962,31 @@
         <f>AD14/$D$14</f>
         <v/>
       </c>
-      <c r="AF14" s="13">
+      <c r="AF14" s="11">
         <f>AG14-AD14</f>
         <v/>
       </c>
-      <c r="AG14" s="13" t="n">
+      <c r="AG14" s="11" t="n">
         <v>741</v>
       </c>
-      <c r="AH14" s="14">
+      <c r="AH14" s="12">
         <f>AG14/$D$14</f>
         <v/>
       </c>
-      <c r="AI14" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 494, Block B: 247</t>
+      <c r="AI14" s="13">
+        <f>AJ14-AG14</f>
+        <v/>
+      </c>
+      <c r="AJ14" s="13" t="n">
+        <v>752</v>
+      </c>
+      <c r="AK14" s="14">
+        <f>AJ14/$D$14</f>
+        <v/>
+      </c>
+      <c r="AL14" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 497 units, Block B: 255 units</t>
         </is>
       </c>
     </row>
@@ -1988,20 +2103,31 @@
         <f>AD15/$D$15</f>
         <v/>
       </c>
-      <c r="AF15" s="13">
+      <c r="AF15" s="11">
         <f>AG15-AD15</f>
         <v/>
       </c>
-      <c r="AG15" s="13" t="n">
+      <c r="AG15" s="11" t="n">
         <v>1394</v>
       </c>
-      <c r="AH15" s="14">
+      <c r="AH15" s="12">
         <f>AG15/$D$15</f>
         <v/>
       </c>
-      <c r="AI15" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 727, Block B: 667</t>
+      <c r="AI15" s="13">
+        <f>AJ15-AG15</f>
+        <v/>
+      </c>
+      <c r="AJ15" s="13" t="n">
+        <v>1396</v>
+      </c>
+      <c r="AK15" s="14">
+        <f>AJ15/$D$15</f>
+        <v/>
+      </c>
+      <c r="AL15" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 728 units, Block B: 668 units</t>
         </is>
       </c>
     </row>
@@ -2118,18 +2244,29 @@
         <f>AD16/$D$16</f>
         <v/>
       </c>
-      <c r="AF16" s="13">
+      <c r="AF16" s="11">
         <f>AG16-AD16</f>
         <v/>
       </c>
-      <c r="AG16" s="13" t="n">
+      <c r="AG16" s="11" t="n">
         <v>906</v>
       </c>
-      <c r="AH16" s="14">
+      <c r="AH16" s="12">
         <f>AG16/$D$16</f>
         <v/>
       </c>
-      <c r="AI16" s="10" t="inlineStr">
+      <c r="AI16" s="13">
+        <f>AJ16-AG16</f>
+        <v/>
+      </c>
+      <c r="AJ16" s="13" t="n">
+        <v>908</v>
+      </c>
+      <c r="AK16" s="14">
+        <f>AJ16/$D$16</f>
+        <v/>
+      </c>
+      <c r="AL16" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2240,10 +2377,13 @@
       <c r="AC17" s="11" t="n"/>
       <c r="AD17" s="11" t="n"/>
       <c r="AE17" s="12" t="n"/>
-      <c r="AF17" s="13" t="n"/>
-      <c r="AG17" s="13" t="n"/>
-      <c r="AH17" s="14" t="n"/>
-      <c r="AI17" s="10" t="inlineStr">
+      <c r="AF17" s="11" t="n"/>
+      <c r="AG17" s="11" t="n"/>
+      <c r="AH17" s="12" t="n"/>
+      <c r="AI17" s="13" t="n"/>
+      <c r="AJ17" s="13" t="n"/>
+      <c r="AK17" s="14" t="n"/>
+      <c r="AL17" s="10" t="inlineStr">
         <is>
           <t>*No info on Teduh, Not obtained AP.</t>
         </is>
@@ -2362,20 +2502,31 @@
         <f>AD18/$D$18</f>
         <v/>
       </c>
-      <c r="AF18" s="13">
+      <c r="AF18" s="11">
         <f>AG18-AD18</f>
         <v/>
       </c>
-      <c r="AG18" s="13" t="n">
+      <c r="AG18" s="11" t="n">
         <v>720</v>
       </c>
-      <c r="AH18" s="14">
+      <c r="AH18" s="12">
         <f>AG18/$D$18</f>
         <v/>
       </c>
-      <c r="AI18" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 436, Block B: 284</t>
+      <c r="AI18" s="13">
+        <f>AJ18-AG18</f>
+        <v/>
+      </c>
+      <c r="AJ18" s="13" t="n">
+        <v>724</v>
+      </c>
+      <c r="AK18" s="14">
+        <f>AJ18/$D$18</f>
+        <v/>
+      </c>
+      <c r="AL18" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 438 units, Block B: 286 units</t>
         </is>
       </c>
     </row>
@@ -2492,20 +2643,31 @@
         <f>AD19/$D$19</f>
         <v/>
       </c>
-      <c r="AF19" s="13">
+      <c r="AF19" s="11">
         <f>AG19-AD19</f>
         <v/>
       </c>
-      <c r="AG19" s="13" t="n">
+      <c r="AG19" s="11" t="n">
         <v>390</v>
       </c>
-      <c r="AH19" s="14">
+      <c r="AH19" s="12">
         <f>AG19/$D$19</f>
         <v/>
       </c>
-      <c r="AI19" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 297, Block B: 93</t>
+      <c r="AI19" s="13">
+        <f>AJ19-AG19</f>
+        <v/>
+      </c>
+      <c r="AJ19" s="13" t="n">
+        <v>390</v>
+      </c>
+      <c r="AK19" s="14">
+        <f>AJ19/$D$19</f>
+        <v/>
+      </c>
+      <c r="AL19" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 297 units, Block B: 93 units</t>
         </is>
       </c>
     </row>
@@ -2622,26 +2784,38 @@
         <f>AD20/$D$20</f>
         <v/>
       </c>
-      <c r="AF20" s="13">
+      <c r="AF20" s="11">
         <f>AG20-AD20</f>
         <v/>
       </c>
-      <c r="AG20" s="13" t="n">
+      <c r="AG20" s="11" t="n">
         <v>296</v>
       </c>
-      <c r="AH20" s="14">
+      <c r="AH20" s="12">
         <f>AG20/$D$20</f>
         <v/>
       </c>
-      <c r="AI20" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 212, Block B: 84</t>
+      <c r="AI20" s="13">
+        <f>AJ20-AG20</f>
+        <v/>
+      </c>
+      <c r="AJ20" s="13" t="n">
+        <v>302</v>
+      </c>
+      <c r="AK20" s="14">
+        <f>AJ20/$D$20</f>
+        <v/>
+      </c>
+      <c r="AL20" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 213 units, Block B: 89 units</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="W3:Y3"/>
+    <mergeCell ref="AI3:AK3"/>
     <mergeCell ref="T3:V3"/>
     <mergeCell ref="AC3:AE3"/>
     <mergeCell ref="AF3:AH3"/>
